--- a/demo_cases/files/missing_required_fields/base_info.xlsx
+++ b/demo_cases/files/missing_required_fields/base_info.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>张明远</t>
+          <t>沈牧舟</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91310000MA1K000001</t>
+          <t>91310115MA1RXH0026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
